--- a/Översikt HERRLJUNGA.xlsx
+++ b/Översikt HERRLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44546</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>44995</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>45072</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44719</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44895</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>46099</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>44719</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45418</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45371</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44529</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>44525</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44497</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44533</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44496</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>44474</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>44474</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>44754</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>44659</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>44790</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>44476</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>44496</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44790</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>44601</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44775</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>44868</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>44834</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>44638</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44502</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>44519</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>44831</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44581</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>44838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44748</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>44847</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44538</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45082</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>44900</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>44900</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>45188</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>44524</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45265</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45172</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45517</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>45327</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>45721</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>45639</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>45306</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45685</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>45770</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>45557</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>44566</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45377</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45365</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>44854</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45285</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>44593</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45051</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45306</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>45335</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>45194</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44525</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>45273</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45098</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>44917</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>44679</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>45491</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>45728</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45085</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45567</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44686</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45562</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>45274</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>45317</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45476</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>45373</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45005</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>44790</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>44958</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>44942</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>45155</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>45155</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>45212</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>44847</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>45350</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45177</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>45176</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45615</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>45763</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44533</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45159</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45660</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45030</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45582</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44914</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45092</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>44860</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45138</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44980</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>45737</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>45763</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>45728</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>45959</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>45756</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44700</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45172</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>45099</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45335</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>45890</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45897</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45266</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>45214</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45664</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45587</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45897</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>45896</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>44847</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>44890</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>45155</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45702</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45265</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>45578</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>45546</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>45546</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>45267</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>45267</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44474</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>45916</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>45918</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>44977</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>45919</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>45567</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45587</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45922</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45922</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45922</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>45321</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45922</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45265</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>45926</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45084</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>44882</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>46142</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45327</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45621</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45933</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45643</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44942</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>45153</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>46149</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>46149</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>44686</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45947</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45947</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45950</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45618</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45315</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44950</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45952</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45952</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45952</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>45957</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45957</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45957</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>45966</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45966</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45425</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45707</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45138</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>45433</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45678</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45453</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45974</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>46154</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>45107</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>45978</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45980</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>45708</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45639</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>45153</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>45163</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>45480</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>45985</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>46154</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>45614</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45985</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45986</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45986</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45303</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>44984</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45986</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45986</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>46029</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>46029</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45989</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45086</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45989</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44904</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45993</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>44524</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>44900</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44659</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45526</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45303</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45622</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45624</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45357</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>45101</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>45337</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45357</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>45723</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>44866</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45149</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45082</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45009</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>46013</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45196</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45705</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45700</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>44917</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45005</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45072</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>45271</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>46031</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>46031</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>46031</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>46031</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>45021</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>46031</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>46031</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>46031</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>46031</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>46035</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45798</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45603</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>44511</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>46036</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>44918</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>46044</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>46043</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45838</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>46043</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>46048</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>44574</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45771</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45771</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>46178</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45277</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>46178</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45756</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45565</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>46064</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>44952</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>46064</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>46182</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>44665</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45400</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>46070</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>46071</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46071</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45527</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45233</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>46182</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>46182</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>44691</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>46072</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44459</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>46079</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>46086</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45077</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44893</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45373</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>46091</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45614</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>46097</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>46097</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>46097</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>46097</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>46099</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>46099</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>46099</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>46196</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45189</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45236</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>44811</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>46114</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45327</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>46119</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>46122</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44551</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45211</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>46120</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44638</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45763</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>46128</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45009</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>46129</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>46130</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45160</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46130</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>46130</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45760</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46130</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>46135</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45219</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45526</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45266</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44890</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>46043</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45222</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>46246</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45468</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>46203</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45888</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>46251</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>45736</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>44733</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>46205</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>46248</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>44644</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45231</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45595</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>46253</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>46188</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45016</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>45021</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45482</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45247</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>45763</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45298</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45546</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>45005</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>44757</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>45168</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>45747</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>44605</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>44908</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45615</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>46267</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>46267</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>44740</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>45713</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>46269</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45277</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>46252</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46272</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>46282</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>46282</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>46282</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>46282</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>45803</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>45803</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>45803</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>45805</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45511</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45810</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45548</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45811</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>45345</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45267</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45337</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>45736</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45726</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45728</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45827</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45736</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45728</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45733</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45833</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45833</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45834</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45841</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45841</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45678</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45839</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44628</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45369</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45386</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45432</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45531</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45371</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>44628</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45587</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>45386</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>44994</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45888</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45266</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>46070</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>46094</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>46097</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>

--- a/Översikt HERRLJUNGA.xlsx
+++ b/Översikt HERRLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44546</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>45072</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44719</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>45418</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>46099</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>44719</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44895</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45371</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44529</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>44525</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>44497</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44473</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44533</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44496</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>44474</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>44474</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>44754</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>44659</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>44790</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>44496</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>44476</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44790</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>44601</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44775</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>44868</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>44638</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>44834</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44502</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>44519</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>44831</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44581</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>44838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44748</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>44847</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44538</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45335</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>45266</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>45527</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45350</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44900</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>44811</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45425</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45373</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45365</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>45317</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>45482</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45468</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>46013</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44984</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45700</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45705</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45160</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>45172</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>44533</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>44942</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45277</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45476</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>45614</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>46031</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>46031</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>46031</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45138</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>46031</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>46031</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>46031</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>45005</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>46031</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>46031</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45756</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45030</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>45890</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>46035</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>46036</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>45303</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>46044</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>45896</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>46043</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>46043</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>45897</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44918</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>46048</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>45021</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44917</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>45803</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>45916</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45664</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>46064</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>46064</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45918</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45005</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>45021</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45803</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45922</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>46070</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>45803</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>45922</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>45922</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45922</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>46072</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>46071</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>46071</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45926</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45805</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44950</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45565</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>46079</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>44860</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45810</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45548</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45587</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>45511</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>45526</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>45526</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>45933</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>46086</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>46091</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>46097</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>46097</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>46097</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>46099</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45763</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>46099</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>46097</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>46099</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45614</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>44679</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>45947</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45950</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>45947</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>45952</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45952</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>45952</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45622</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>45957</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>45005</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45957</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>45957</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>46114</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>46119</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>45273</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>46120</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>46122</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>45966</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45567</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>44890</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>44757</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>44958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>45480</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>45811</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>44644</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>45639</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45345</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>46128</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>45978</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45974</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45615</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>46130</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>46130</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>46130</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>45980</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>46129</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>46130</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>44977</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45985</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>45986</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>45986</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>45985</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>46029</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>46029</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>45986</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>46135</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45099</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>45989</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45265</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>45897</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45989</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45267</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45993</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45149</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>45763</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45337</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45155</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>46043</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45713</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45959</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45172</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45737</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45728</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45770</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45077</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>44790</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>44866</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>45733</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>45736</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>45728</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45072</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>46142</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45736</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45827</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>44524</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45517</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45266</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45233</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45085</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45084</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44900</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>44882</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45098</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>46149</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>46149</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45721</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45771</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45771</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>46154</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45833</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45833</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45763</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>46154</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45834</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>44908</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44914</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>45222</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45841</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45841</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45723</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44511</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>44952</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>45357</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45357</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45678</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45107</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45247</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45702</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45277</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45327</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>45603</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45838</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>45168</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>45798</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45163</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>45051</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45453</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>44574</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>45578</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>46178</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44524</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>45707</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>46178</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>46182</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>46182</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>46182</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45176</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45009</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45595</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45189</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45582</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44525</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45092</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45763</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>45567</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>44551</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>45839</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>46196</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45337</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44847</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>46203</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44593</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45196</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45888</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>46205</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45082</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45194</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44665</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45101</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45615</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>46251</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>46253</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>46188</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45660</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>44740</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44686</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45685</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>44638</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45155</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45621</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44900</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45236</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44686</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45188</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45303</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44700</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45756</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45265</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>46267</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>46267</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46269</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45327</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45271</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46272</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>46252</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45747</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45736</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45285</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45562</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45298</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45219</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45335</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>46282</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>46282</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>46282</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>46282</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>45546</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>44917</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>46286</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>44854</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45546</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45546</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44890</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45265</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>45155</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44605</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>45231</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>46288</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>44659</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>45177</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>45153</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45708</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44474</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>46248</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>46246</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>45624</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44691</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>45214</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>45009</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45153</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45016</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>44566</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>45433</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44980</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>44942</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45491</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>44733</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>45138</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26663,7 +26663,7 @@
         <v>45377</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -26736,7 +26736,7 @@
         <v>45086</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>45306</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>45267</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45267</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45315</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>45728</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45306</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44893</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45159</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45678</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45587</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>45639</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27617,7 +27617,7 @@
         <v>45211</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>45321</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45212</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45618</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45373</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45327</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45082</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44904</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45643</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45557</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45760</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45400</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45274</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>44628</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44628</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>45369</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45386</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>45432</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>45531</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45371</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45587</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45386</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44994</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45888</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45266</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>46070</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>46094</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>46097</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>

--- a/Översikt HERRLJUNGA.xlsx
+++ b/Översikt HERRLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44546</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>45072</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44719</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>45418</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>46099</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>44719</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44895</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45371</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44529</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>44525</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>44497</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44473</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44533</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44496</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>44474</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>44474</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>44754</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>44659</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>44790</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>44496</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>44476</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44790</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>44601</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44775</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>44868</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>44638</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>44834</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44502</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>44519</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>44831</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44581</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>44838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44748</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>44847</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44538</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45335</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>45266</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>45527</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45350</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44900</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>44811</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45425</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45373</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44847</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45365</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>45317</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>45482</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45468</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>46013</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44984</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45700</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45705</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45160</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>45172</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>44533</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>44942</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45277</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45476</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>45614</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>46031</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>46031</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>46031</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45138</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>46031</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>46031</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>46031</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>45005</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>46031</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>46031</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45756</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45030</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>45890</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>46035</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>46036</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>45303</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>46044</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>45896</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>46043</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>46043</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>45897</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44918</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>46048</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>45021</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44917</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>45803</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>45916</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45664</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>46064</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>46064</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45918</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45005</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>45021</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45803</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45922</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>46070</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>45803</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>45922</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>45922</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45922</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>46072</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>46071</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>46071</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45926</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45805</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44950</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45565</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>46079</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>44860</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45810</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45548</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45587</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>45511</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>45526</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>45526</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>45933</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>46086</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>46091</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>46097</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>46097</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>46097</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>46099</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45763</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>46099</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>46097</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>46099</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45614</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>44679</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>45947</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45950</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>45947</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>45952</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45952</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>45952</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45622</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>45957</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>45005</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45957</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>45957</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>46114</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>46119</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>45273</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>46120</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>46122</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>45966</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45567</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>44890</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>44757</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>44958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>45480</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>45811</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>44644</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>45639</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45345</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>46128</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>45978</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45974</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45615</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>46130</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>46130</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>46130</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>45980</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>46129</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>46130</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>44977</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45985</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>45986</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>45986</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>45985</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>46029</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>46029</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>45986</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>46135</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45099</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>45989</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45265</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>45897</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45989</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45267</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45993</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45149</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>45763</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45337</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45155</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>46043</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45713</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45959</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45172</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45737</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45728</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45770</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45077</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>44790</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>44866</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>45733</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>45736</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>45728</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45072</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>46142</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45736</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45827</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>44524</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45517</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45266</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45233</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45085</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45084</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44900</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>44882</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45098</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>46149</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>46149</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45721</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45771</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45771</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>46154</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45833</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45833</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45763</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>46154</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45834</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>44908</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44914</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>45222</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45841</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45841</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45723</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44511</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>44952</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>45357</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45357</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45678</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45107</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45247</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45702</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45277</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45327</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>45603</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45838</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>45168</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>45798</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45163</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>45051</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45453</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>44574</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>45578</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>46178</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44524</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>45707</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>46178</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>46182</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>46182</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>46182</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45176</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45009</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45595</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45189</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45582</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44525</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45092</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45763</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>45567</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>44551</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>45839</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>46196</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45337</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44847</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>46203</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44593</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45196</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45888</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>46205</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45082</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45194</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44665</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45101</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45615</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>46251</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>46253</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>46188</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45660</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>44740</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44686</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45685</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>44638</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45155</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45621</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44900</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45236</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44686</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45188</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45303</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44700</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45756</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45265</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>46267</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>46267</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46269</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45327</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45271</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46272</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>46252</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45747</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45736</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45285</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45562</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45298</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45219</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45335</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>46282</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>46282</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>46282</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>46282</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>45546</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>44917</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>46286</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>44854</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45546</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45546</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44890</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45265</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>45155</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44605</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>45231</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>46288</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>44659</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>45177</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>45153</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45708</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44474</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>46248</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>46246</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>45624</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44691</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>45214</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>45009</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45153</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45016</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>44566</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>45433</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44980</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>44942</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45491</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>44733</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>45138</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26663,7 +26663,7 @@
         <v>45377</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -26736,7 +26736,7 @@
         <v>45086</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>45306</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>45267</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45267</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45315</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>45728</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45306</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44893</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45159</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45678</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45587</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>45639</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27617,7 +27617,7 @@
         <v>45211</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>45321</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45212</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45618</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45373</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45327</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45082</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44904</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45643</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45557</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45760</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45400</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45274</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>44628</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44628</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>45369</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45386</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>45432</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>45531</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45371</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45587</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45386</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44994</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45888</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45266</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>46070</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>46094</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>46097</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>

--- a/Översikt HERRLJUNGA.xlsx
+++ b/Översikt HERRLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44546</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>44995</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>45072</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44719</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44895</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>45418</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44719</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45371</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44529</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>44525</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44497</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44533</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44496</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>44474</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>44474</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>44754</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>44659</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>44790</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>44476</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>44496</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44601</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>44790</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44775</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>44868</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>44638</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>44834</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44519</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>44502</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>44831</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44581</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>44838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44748</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>44847</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44538</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45082</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>44900</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>44900</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>44524</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>45188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45265</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45517</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>45172</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>45377</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44847</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45327</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45721</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>45639</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>45306</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45685</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45770</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>44566</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45557</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>46013</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>45138</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>45705</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>45700</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>45365</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>45756</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>44854</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>45890</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>44593</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>46031</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>45897</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46031</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45896</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>46031</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>46031</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>45285</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45051</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>46031</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>46031</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>46031</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>46031</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>46035</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45306</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>45335</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>46036</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>46044</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>46043</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>44525</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>46043</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>45194</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>46048</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>45916</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>45098</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45918</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>45803</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>45803</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45273</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45805</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>45922</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45922</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45922</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45922</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44917</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>45926</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>45491</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45085</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>44679</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>45728</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>45511</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45567</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45933</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>46064</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>46064</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>46070</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>46071</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>46071</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44686</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45274</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>46072</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>45562</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>45810</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>45947</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45548</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45947</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>45317</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45811</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45950</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>46079</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>45476</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45952</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>45952</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>45952</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45957</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>45957</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>46086</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45957</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>45373</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>45005</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>44790</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>45345</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>46091</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44958</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>45267</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45966</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>44942</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>46097</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46097</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>46097</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>45155</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>45155</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>46097</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>46099</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>46099</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>46099</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45337</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45212</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>45350</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45974</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44847</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45177</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45978</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>45980</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45985</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>44533</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>45985</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>45986</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>45986</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>46114</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45176</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>45615</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>45763</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45986</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>46029</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>46029</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45989</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45159</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>45989</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>45660</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>46119</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>46122</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>45030</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45993</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>45736</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>46120</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45728</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45827</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45582</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>44914</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45092</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45728</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>44860</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45733</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>46128</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44980</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>46129</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>46130</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>46130</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>46130</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>46130</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45833</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>44700</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>46135</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45099</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45335</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45833</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45834</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45266</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45214</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45664</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45587</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>46043</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>44890</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>45841</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>45155</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45841</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45578</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45546</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45546</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45267</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45267</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44474</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45737</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>45763</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45728</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45959</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44977</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>45567</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>45897</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45587</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45321</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45265</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45678</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45084</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44882</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45265</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>45327</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45621</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>45643</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44942</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>45153</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>44686</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>46142</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>45618</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45315</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>46149</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>46149</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>46154</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>46154</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45425</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45707</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45138</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>45433</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45678</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45453</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45107</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45357</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45639</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45357</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45723</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45153</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45163</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45480</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45614</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45303</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44984</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45839</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45086</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45798</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45603</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44904</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45838</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>46178</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>44524</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44900</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>45172</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>46178</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44659</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45526</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>46182</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>46182</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>46182</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45303</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45622</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45624</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45101</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>45337</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>44866</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>45149</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>45082</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45009</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>46196</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>45196</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>44917</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>45005</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>45072</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45271</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45021</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>46203</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45888</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>46205</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44511</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>44918</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>46188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44574</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45771</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45771</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45277</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45756</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45565</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>44952</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>46267</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>46267</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>44665</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45400</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>46269</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45527</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45233</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>44691</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>46272</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45077</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44893</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45373</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>46282</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>46282</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>46282</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45614</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>46282</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45189</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45236</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>46286</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44811</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>46288</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>45327</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>46246</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>44551</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>45211</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45708</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44638</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>46248</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45763</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45009</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45160</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>45760</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>46295</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>46252</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45219</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45526</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>46251</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45266</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44890</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>46294</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>45222</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>46294</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>45468</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>45803</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45702</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45736</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44733</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>46296</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>46295</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>46253</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>44644</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>45231</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45595</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>45016</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>45021</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45482</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45247</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>45763</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45298</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>45546</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45005</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44757</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>45168</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45747</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>44605</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>44908</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45615</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44740</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45713</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45277</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>44628</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>45369</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45386</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45432</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45531</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45371</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>44628</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45587</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45386</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>44994</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45888</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45266</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>46070</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>46094</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>46097</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>

--- a/Översikt HERRLJUNGA.xlsx
+++ b/Översikt HERRLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44546</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>44995</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>45072</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44719</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>44895</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>45418</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44719</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45371</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44529</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>44525</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44497</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44533</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44496</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>44474</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>44474</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>44754</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>44659</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>44790</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>44476</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>44496</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44601</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>44790</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44775</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>44868</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>44638</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>44834</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44519</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>44502</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>44831</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44581</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>44838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44748</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>44847</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44538</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45082</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>44900</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>44900</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>44524</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>45188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45265</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45517</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>45172</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>45377</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44847</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45327</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45721</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>45639</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>45306</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45685</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45770</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>44566</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45557</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>46013</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>45138</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>45705</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>45700</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>45365</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>45756</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>44854</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>45890</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>44593</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>46031</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>45897</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46031</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45896</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>46031</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>46031</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>45285</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45051</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>46031</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>46031</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>46031</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>46031</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>46035</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45306</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>45335</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>46036</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>46044</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>46043</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>44525</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>46043</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>45194</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>46048</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>45916</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>45098</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45918</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>45803</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>45803</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45273</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45805</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>45922</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45922</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45922</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45922</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44917</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>45926</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>45491</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45085</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>44679</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>45728</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>45511</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45567</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45933</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>46064</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>46064</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>46070</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>46071</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>46071</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44686</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45274</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>46072</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>45562</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>45810</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>45947</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45548</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45947</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>45317</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45811</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45950</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>46079</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>45476</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45952</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>45952</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>45952</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45957</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>45957</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>46086</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45957</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>45373</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>45005</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>44790</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>45345</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>46091</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44958</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>45267</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45966</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>44942</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>46097</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46097</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>46097</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>45155</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>45155</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>46097</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>46099</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>46099</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>46099</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45337</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45212</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>45350</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45974</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44847</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45177</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45978</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>45980</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45985</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>44533</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>45985</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>45986</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>45986</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>46114</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45176</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>45615</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>45763</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45986</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>46029</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>46029</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45989</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45159</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>45989</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>45660</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>46119</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>46122</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>45030</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45993</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>45736</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>46120</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45728</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45827</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45582</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>44914</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45092</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45728</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>44860</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45733</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>46128</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44980</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>46129</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>46130</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>46130</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>46130</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>46130</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45833</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>44700</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>46135</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45099</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45335</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45833</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45834</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45266</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45214</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45664</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45587</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>46043</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>44890</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>45841</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>45155</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45841</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45578</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45546</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45546</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45267</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45267</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44474</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45737</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>45763</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45728</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45959</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44977</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>45567</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>45897</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45587</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45321</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45265</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45678</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45084</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44882</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45265</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>45327</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45621</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>45643</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44942</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>45153</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>44686</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>46142</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>45618</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45315</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>46149</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>46149</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>46154</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>46154</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45425</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45707</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45138</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>45433</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45678</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45453</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45107</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45357</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45639</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45357</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45723</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45153</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45163</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45480</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45614</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45303</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44984</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45839</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45086</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45798</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45603</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44904</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45838</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>46178</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>44524</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44900</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>45172</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>46178</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44659</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45526</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>46182</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>46182</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>46182</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45303</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45622</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45624</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45101</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>45337</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>44866</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>45149</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>45082</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45009</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>46196</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>45196</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>44917</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>45005</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>45072</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45271</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45021</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>46203</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45888</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>46205</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44511</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>44918</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>46188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44574</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45771</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45771</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45277</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45756</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45565</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>44952</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>46267</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>46267</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>44665</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45400</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>46269</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45527</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45233</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>44691</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>46272</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45077</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44893</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45373</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>46282</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>46282</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>46282</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45614</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>46282</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45189</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45236</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>46286</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44811</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>46288</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>45327</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>46246</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>44551</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>45211</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45708</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44638</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>46248</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45763</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45009</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45160</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>45760</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>46295</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>46252</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45219</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45526</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>46251</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45266</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44890</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>46294</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>45222</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>46294</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>45468</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>45803</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45702</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45736</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44733</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>46296</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>46295</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>46253</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>44644</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>45231</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45595</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>45016</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>45021</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45482</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45247</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>45763</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45298</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>45546</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45005</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44757</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>45168</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45747</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>44605</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>44908</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45615</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44740</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45713</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45277</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>44628</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>45369</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45386</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45432</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45531</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45371</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>44628</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45587</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45386</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>44994</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45888</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45266</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>46070</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>46094</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>46097</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>

--- a/Översikt HERRLJUNGA.xlsx
+++ b/Översikt HERRLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44546</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>44995</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>45072</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44719</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>45418</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44719</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44895</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45371</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44525</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>44529</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>44497</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44533</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44496</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44754</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>44659</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>44790</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>44638</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>44496</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>44834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>44581</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>44838</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44790</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>44538</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44601</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>44748</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44775</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>44847</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>44831</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44868</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>44900</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>44900</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44882</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45138</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>45098</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>45721</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45771</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>45350</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45377</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45373</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45425</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44847</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>45763</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44908</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45086</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>45306</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44914</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45222</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45335</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45266</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>45267</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45267</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>45315</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45728</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45527</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>45365</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44811</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>45317</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>44847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44952</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45306</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>44893</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>45482</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45468</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>45159</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>45678</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>45107</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>45587</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>45639</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>44984</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>45211</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>45321</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>45172</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45212</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>45618</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>45247</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45138</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>45277</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45373</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>45327</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>45160</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>45168</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45756</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>45163</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44533</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45051</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44942</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45277</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45890</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>45327</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45082</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>45476</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>45614</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>44904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>45453</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>45643</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>45896</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>45897</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>45005</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45030</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>45557</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45760</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>44574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>45303</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>45400</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>45578</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>44918</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>44524</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>45274</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45707</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>45176</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>45021</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>45009</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>45916</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>44917</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45595</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>45918</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>45189</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>45582</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>45664</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45005</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>45021</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45922</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44525</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>45922</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>45922</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>45922</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45926</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45092</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45763</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44950</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>45567</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45565</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44551</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44860</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45587</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>45337</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>45526</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45526</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45933</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>44593</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45803</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>45082</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>45803</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45763</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>45805</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45194</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44665</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>45810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45614</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>44679</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45101</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45548</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45511</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45615</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45811</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>45660</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45345</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>44740</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45005</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45267</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>45337</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45947</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45950</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>45273</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>45947</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44686</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45685</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>44638</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45155</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45621</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45567</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44890</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45952</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45733</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45736</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45728</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44757</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>44958</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45480</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45827</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45728</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45952</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>45952</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44900</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>44644</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45639</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45957</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45957</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45957</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45833</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45833</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>45834</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45615</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>45236</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44686</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>44977</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>45188</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>45841</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>45841</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45303</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>44700</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45099</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45756</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45149</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45678</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>45974</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45265</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45327</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45980</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>45155</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>45713</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45271</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>45172</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>45747</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45839</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>45736</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>45770</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>46097</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>45285</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>46099</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>46099</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>46097</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45562</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45077</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45985</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>46099</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45298</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45986</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45219</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>44790</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45335</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>44866</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45986</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45986</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45985</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45072</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>46029</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>44524</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45517</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>45546</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>46029</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>45986</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45989</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>45266</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>44917</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45989</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45233</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45085</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>46114</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45084</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>44854</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>46119</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45993</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>46120</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45546</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45546</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>46122</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>44890</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>46128</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45265</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>46130</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>46130</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>46130</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45155</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44605</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>46129</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>46130</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45231</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>44659</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>46135</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45177</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45153</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45265</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45897</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>46013</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45700</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45705</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45624</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>44691</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45214</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45009</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45763</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>46031</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>46031</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>46031</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>46031</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>46031</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>46031</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45153</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>46031</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>46031</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45016</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>46043</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>46035</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>46036</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>46044</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>45959</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45737</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>46043</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>46043</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45728</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>44566</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45433</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44980</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>46048</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>44942</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45491</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>46142</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>46064</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>46064</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>46070</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>46149</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>46149</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>46072</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>46154</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>46079</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>46154</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>46086</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>46091</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>46097</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>46097</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45723</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45357</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45357</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>45603</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45838</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45798</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>46178</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>46178</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>46182</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>46182</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>46182</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>46196</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>46203</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45888</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>46205</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46188</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>46267</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>46267</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>46269</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>46272</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>46282</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>46282</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>46282</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>46282</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>46286</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>46288</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45708</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>46246</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>46294</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>46294</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>46248</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>46253</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>46296</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>46295</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>46251</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>46295</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>46252</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>46071</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45702</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>45966</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45803</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>46301</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>46304</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>46303</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44628</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44628</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45369</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45386</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45432</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45531</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45371</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>45587</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45386</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44994</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45888</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45266</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>46070</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>46094</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>46097</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>

--- a/Översikt HERRLJUNGA.xlsx
+++ b/Översikt HERRLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44546</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>44995</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>45072</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44719</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>45418</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44719</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44895</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45371</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44525</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>44529</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>44497</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44533</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>44496</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44754</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>44659</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>44790</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>44638</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>44496</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>44834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>44581</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>44838</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44790</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>44538</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44601</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>44748</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44775</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>44847</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>44831</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44868</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>44900</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>44900</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44882</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45138</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>45098</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>45721</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45771</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>45350</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45377</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45373</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45425</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44847</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>45763</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44908</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45086</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>45306</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44914</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45222</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45335</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45266</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>45267</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45267</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>45315</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45728</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45527</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>45365</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44811</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>45317</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>44847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44952</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45306</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>44893</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>45482</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45468</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>45159</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>45678</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>45107</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>45587</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>45639</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>44984</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>45211</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>45321</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>45172</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45212</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>45618</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>45247</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45138</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>45277</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45373</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>45327</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>45160</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>45168</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45756</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>45163</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44533</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45051</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44942</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45277</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45890</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>45327</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45082</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>45476</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>45614</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>44904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>45453</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>45643</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>45896</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>45897</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>45005</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45030</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>45557</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45760</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>44574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>45303</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>45400</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>45578</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>44918</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>44524</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>45274</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45707</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>45176</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>45021</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>45009</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>45916</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>44917</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45595</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>45918</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>45189</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>45582</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>45664</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45005</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>45021</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45922</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44525</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>45922</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>45922</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>45922</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45926</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45092</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45763</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44950</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>45567</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45565</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44551</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44860</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45587</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>45337</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>45526</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45526</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45933</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>44593</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45803</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>45082</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>45803</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45763</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>45805</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45194</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44665</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>45810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45614</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>44679</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45101</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45548</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45511</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45615</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45811</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>45660</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45345</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>44740</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45005</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45267</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>45337</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45947</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45950</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>45273</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>45947</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44686</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45685</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>44638</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45155</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45621</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45567</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44890</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45952</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45733</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45736</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45728</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44757</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>44958</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45480</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45827</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45728</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45952</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>45952</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44900</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>44644</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45639</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45957</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45957</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45957</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45833</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45833</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>45834</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45615</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>45236</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44686</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>44977</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>45188</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>45841</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>45841</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45303</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>44700</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45099</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45756</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45149</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45678</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>45974</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45265</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45327</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45980</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>45155</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>45713</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45271</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>45172</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>45747</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45839</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>45736</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>45770</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>46097</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>45285</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>46099</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>46099</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>46097</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45562</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45077</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45985</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>46099</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45298</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45986</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45219</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>44790</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45335</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>44866</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45986</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45986</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45985</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45072</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>46029</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>44524</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45517</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>45546</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>46029</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>45986</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45989</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>45266</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>44917</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45989</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45233</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45085</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>46114</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45084</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>44854</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>46119</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45993</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>46120</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45546</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45546</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>46122</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>44890</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>46128</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45265</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>46130</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>46130</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>46130</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45155</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44605</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>46129</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>46130</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45231</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>44659</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>46135</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45177</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45153</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45265</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45897</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>46013</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45700</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45705</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45624</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>44691</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45214</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45009</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45763</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>46031</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>46031</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>46031</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>46031</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>46031</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>46031</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45153</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>46031</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>46031</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45016</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>46043</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>46035</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>46036</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>46044</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>45959</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45737</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>46043</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>46043</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45728</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>44566</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45433</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44980</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>46048</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>44942</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45491</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>46142</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>46064</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>46064</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>46070</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>46149</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>46149</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>46072</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>46154</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>46079</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>46154</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>46086</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>46091</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>46097</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>46097</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45723</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45357</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45357</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>45603</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45838</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45798</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>46178</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>46178</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>46182</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>46182</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>46182</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>46196</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>46203</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45888</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>46205</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46188</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>46267</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>46267</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>46269</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>46272</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>46282</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>46282</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>46282</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>46282</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>46286</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>46288</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45708</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>46246</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>46294</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>46294</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>46248</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>46253</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>46296</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>46295</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>46251</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>46295</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>46252</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>46071</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45702</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>45966</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45803</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>46301</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>46304</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>46303</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44628</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44628</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45369</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45386</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45432</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45531</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45371</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>45587</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45386</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44994</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45888</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45266</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>46070</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>46094</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>46097</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>

--- a/Översikt HERRLJUNGA.xlsx
+++ b/Översikt HERRLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44546</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44995</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>45072</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44719</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44895</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>46099</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44719</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>45418</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45371</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44529</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44525</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>44497</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44533</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44496</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44754</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44659</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44790</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44790</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44601</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44775</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44868</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44638</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44834</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44519</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44831</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44748</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44538</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45082</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44900</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44900</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44524</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>45188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>45265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>45172</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45517</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>45377</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>45639</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45306</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>45685</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44566</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45770</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45557</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45365</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45327</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>44854</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45285</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45051</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44593</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45306</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>45335</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45194</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>44525</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45721</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>45273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45098</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44917</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44679</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45728</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>45491</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45567</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45085</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44686</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>45562</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45274</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45317</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45476</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45373</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45005</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>44790</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44958</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>44942</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45155</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45155</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44847</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45212</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45350</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45177</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44533</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>45176</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45615</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45763</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45159</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45660</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45737</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45763</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45728</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>45959</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45030</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45138</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>45897</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45582</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45756</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>45172</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44914</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>45092</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44860</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45890</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44980</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>45897</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45896</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>44847</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44700</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45265</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45099</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45335</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45266</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>45214</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45664</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>45587</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44890</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>46142</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>45155</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45916</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45918</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45578</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45922</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>45922</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>45922</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>45546</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>45546</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>45267</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>45267</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45922</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>46149</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>46149</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45926</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44977</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>45933</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45567</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>45587</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>45321</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45265</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45084</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>44882</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>45327</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>45947</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>45947</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>45621</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45950</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>45643</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>45952</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>45952</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>46154</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>45952</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>45957</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>45957</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>46154</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>45957</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>44942</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>45153</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>44686</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>45618</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>45315</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>44950</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>45974</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>45978</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>45980</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45357</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>45985</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45985</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>45986</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45357</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45986</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45723</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45425</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45986</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45986</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>46029</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45707</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46029</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>45989</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45989</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45138</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45993</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45433</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45678</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45453</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45107</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45639</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45153</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45163</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45480</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45614</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45303</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>44984</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45798</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45603</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45086</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44904</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>46013</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>45705</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>45700</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>44524</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>44900</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45838</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>44659</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>45526</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>46031</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>46031</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>46031</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>46031</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45303</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>46031</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>46031</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>46031</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>46031</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>45622</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45624</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45101</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>46035</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>46036</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>46178</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>46044</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>46178</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>46043</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45337</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44866</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>46043</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>46182</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>46048</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45149</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45082</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45009</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>46182</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>46182</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45196</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>44917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>46064</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>46064</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45005</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45072</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45271</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>46070</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>46072</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45021</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>46079</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>44511</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46086</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44918</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>46091</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>46097</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>46097</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>46097</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>46097</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>46099</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>46099</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44574</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>46099</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45771</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45771</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>46196</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45277</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>46114</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45756</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45565</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44952</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>46119</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>46122</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>44665</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45400</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>46120</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45527</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45233</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>44691</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>46128</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>46129</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>46130</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>46130</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>46130</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>46130</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>46135</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>46203</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>45888</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>45077</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>44893</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45373</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>46043</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>46205</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
         <v>45614</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>46188</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>45189</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>45236</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44811</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45327</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44551</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>45211</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>44638</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>46272</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>45763</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45009</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45160</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45760</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45219</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45526</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45266</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>44890</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45222</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45468</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>46282</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>46282</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>46282</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>46282</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45736</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44733</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>44644</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45231</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>45595</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>46286</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46288</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45016</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>45021</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45482</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45247</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>46246</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>45763</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45298</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>45708</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>46248</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45546</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>45005</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44757</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>45168</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45747</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44605</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>46295</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44908</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45615</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>46252</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>46251</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46294</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>46294</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>44740</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45803</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>45702</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>46296</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>46295</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45713</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>46253</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45277</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>46301</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>46071</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>45966</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>46303</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>46304</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>45803</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45803</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45805</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46267</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45511</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45810</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45548</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>45811</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>46269</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>45345</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>45267</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>46267</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45337</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>46310</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45736</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45728</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45827</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>45728</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>45733</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>45833</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45833</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45834</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>45841</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45841</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45678</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45839</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>44628</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45369</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>45386</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>45432</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45531</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>45371</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>44628</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>45587</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45386</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44994</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>45888</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45266</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>46070</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>46094</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>46097</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>

--- a/Översikt HERRLJUNGA.xlsx
+++ b/Översikt HERRLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44546</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44995</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>45072</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44719</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44895</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>46099</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>44719</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>45418</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45371</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44529</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44525</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>44497</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44533</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44496</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44754</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44659</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44790</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44790</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44601</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44775</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44868</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44638</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44834</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44519</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44831</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44748</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44538</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45082</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44900</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44900</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44524</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>45188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>45265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>45172</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45517</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>45377</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>45639</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45306</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>45685</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44566</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45770</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45557</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45365</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45327</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>44854</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45285</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45051</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44593</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45306</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>45335</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45194</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>44525</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45721</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>45273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45098</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44917</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44679</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45728</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>45491</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45567</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45085</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44686</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>45562</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45274</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45317</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45476</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45373</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45005</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>44790</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44958</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>44942</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45155</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45155</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44847</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45212</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45350</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45177</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44533</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>45176</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45615</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45763</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45159</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45660</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45737</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45763</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45728</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>45959</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45030</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45138</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>45897</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45582</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45756</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>45172</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44914</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>45092</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44860</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45890</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44980</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>45897</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45896</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>44847</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44700</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45265</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45099</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45335</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45266</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>45214</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45664</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>45587</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44890</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>46142</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>45155</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45916</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45918</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45578</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45922</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>45922</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>45922</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>45546</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>45546</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>45267</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>45267</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45922</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>46149</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>46149</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45926</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44977</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>45933</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45567</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>45587</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>45321</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45265</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45084</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>44882</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>45327</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>45947</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>45947</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>45621</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45950</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>45643</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>45952</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>45952</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>46154</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>45952</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>45957</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>45957</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>46154</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>45957</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>44942</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>45153</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>44686</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>45618</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>45315</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>44950</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>45974</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>45978</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>45980</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45357</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>45985</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45985</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>45986</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45357</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45986</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45723</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45425</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45986</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45986</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>46029</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45707</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46029</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>45989</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45989</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45138</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45993</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45433</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45678</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45453</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45107</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45639</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45153</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45163</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45480</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45614</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45303</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>44984</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45798</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45603</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45086</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44904</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>46013</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>45705</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>45700</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>44524</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>44900</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45838</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>44659</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>45526</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>46031</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>46031</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>46031</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>46031</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45303</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>46031</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>46031</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>46031</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>46031</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>45622</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45624</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45101</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>46035</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>46036</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>46178</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>46044</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>46178</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>46043</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45337</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44866</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>46043</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>46182</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>46048</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45149</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45082</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45009</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>46182</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>46182</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45196</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>44917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>46064</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>46064</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45005</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45072</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45271</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>46070</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>46072</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45021</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>46079</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>44511</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46086</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44918</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>46091</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>46097</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>46097</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>46097</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>46097</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>46099</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>46099</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44574</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>46099</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45771</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45771</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>46196</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45277</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>46114</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45756</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45565</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44952</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>46119</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>46122</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>44665</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45400</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>46120</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45527</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45233</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>44691</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>46128</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>46129</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>46130</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>46130</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>46130</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>46130</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>46135</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>46203</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>45888</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>45077</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>44893</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45373</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>46043</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>46205</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
         <v>45614</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>46188</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>45189</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>45236</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44811</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45327</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44551</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>45211</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>44638</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>46272</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>45763</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45009</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45160</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45760</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45219</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45526</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45266</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>44890</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45222</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45468</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>46282</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>46282</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>46282</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>46282</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45736</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44733</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>44644</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45231</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>45595</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>46286</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46288</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45016</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>45021</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45482</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45247</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>46246</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>45763</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45298</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>45708</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>46248</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45546</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>45005</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44757</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>45168</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45747</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44605</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>46295</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44908</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45615</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>46252</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>46251</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46294</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>46294</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>44740</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45803</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>45702</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>46296</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>46295</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45713</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>46253</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45277</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>46301</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>46071</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>45966</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>46303</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>46304</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>45803</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45803</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45805</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46267</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45511</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45810</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45548</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>45811</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>46269</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>45345</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>45267</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>46267</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45337</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>46310</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45736</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45728</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45827</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>45728</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>45733</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>45833</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45833</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45834</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>45841</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45841</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45678</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45839</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>44628</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45369</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>45386</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>45432</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45531</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>45371</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>44628</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>45587</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45386</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44994</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>45888</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45266</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>46070</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>46094</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>46097</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>

--- a/Översikt HERRLJUNGA.xlsx
+++ b/Översikt HERRLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44546</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44995</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>45072</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44719</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44895</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>45418</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>44719</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45371</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44529</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44525</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>44497</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44533</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44496</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44754</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44659</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44790</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44790</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44601</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44775</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44868</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44638</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44834</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44502</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44519</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44831</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44748</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44538</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45138</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>45756</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44659</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>45350</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45890</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>45335</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45896</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45177</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45153</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45266</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45527</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44811</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45172</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>44900</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>45624</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>44691</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45214</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45009</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45916</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>45723</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45153</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45918</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>45016</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>45357</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45922</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>45922</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45922</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>45922</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45357</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45926</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>44566</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45433</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45603</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45838</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45798</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44980</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45933</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>44942</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44733</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45373</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45425</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>44847</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45138</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>46178</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45365</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45377</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45947</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45950</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45947</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>45086</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45952</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45306</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>46178</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>45952</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45952</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>46182</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>46182</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>46182</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45957</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45957</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45957</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45267</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45267</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45315</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45728</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45317</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>45306</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>44893</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>45159</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>45678</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>46196</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>45587</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45639</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>45978</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>45211</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>45974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>45321</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>45212</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>45618</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>45482</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>45980</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45373</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45468</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>46203</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45327</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45082</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>45985</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>45986</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>45888</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>44904</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>46205</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45986</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45986</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>45643</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45985</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>46029</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>46029</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>45986</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>45989</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>46188</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>45989</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>45993</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>44984</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>45557</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>45760</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>45400</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>45274</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>46013</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>45700</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>45705</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>46282</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>46282</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>46282</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>46031</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>46031</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>46031</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>46031</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>46031</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>46031</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>46031</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>46031</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>46286</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>46035</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>46036</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>46044</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>46043</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>46048</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>45160</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>46288</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>45803</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>45805</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>45708</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45810</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>46246</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>45548</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>45511</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>46294</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>46064</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>46064</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>44533</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>45811</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44942</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>46294</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45345</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>46248</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>46070</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45267</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45337</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>46072</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>46253</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>46296</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45277</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>46295</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>46251</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>46079</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45733</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45736</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>45728</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>45827</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>45728</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>46295</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>46252</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>46071</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>45702</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45476</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45833</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45833</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>46086</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>45834</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45966</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>46091</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>45614</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>46097</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45803</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>46097</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>46097</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>46099</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>46099</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>46097</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>45841</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45841</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>46099</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>45005</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>46301</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>45030</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>45678</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>46114</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>46119</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>46120</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>46304</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>46122</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>46303</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>46128</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>45839</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>45303</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>46130</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>46130</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>46130</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>46129</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>46130</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>44847</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>44918</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45021</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>44917</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>46135</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45265</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>46310</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45897</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>46267</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45664</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45005</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45021</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>46269</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>46267</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45763</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>46272</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>46043</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>44950</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45959</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45565</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>45737</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>46316</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>45728</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>46280</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>46280</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>44860</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>46316</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>46316</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>46280</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>45587</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>45526</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45526</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>46282</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>46142</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>46043</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         <v>45763</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45614</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>46149</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>46149</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44679</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>46154</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45622</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>46154</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45005</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>45273</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45567</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>44890</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>44757</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>44958</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45480</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>44644</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45639</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45615</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>44977</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45099</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45149</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45155</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45713</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45172</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45770</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45077</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>44790</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>44866</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45072</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44524</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45517</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45266</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45233</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45085</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>45084</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>44900</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44882</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45098</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45721</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45771</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45771</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45763</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44908</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44914</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45222</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>44511</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>44952</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>45107</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45247</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>45277</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45327</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45168</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>45163</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>45051</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45453</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>44574</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>45578</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>44524</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>45707</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45176</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45009</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>45595</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45189</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45582</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44525</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45092</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>45763</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45567</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>44551</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45337</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44593</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45196</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45082</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45194</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44665</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45101</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45615</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45660</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44740</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>44686</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>45685</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>44638</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45155</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45621</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>44900</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>45236</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>44686</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45188</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45303</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>44700</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>45756</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45265</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45327</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45271</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>45747</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45736</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45285</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>45562</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>45298</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45219</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45335</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>45546</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>44917</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>44854</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45546</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>45546</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>44890</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>45265</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>45155</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>44605</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>45231</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44628</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>44628</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45369</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45386</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45432</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45531</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45371</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45587</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>45386</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44994</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45888</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45266</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>46070</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>46094</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>46097</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>

--- a/Översikt HERRLJUNGA.xlsx
+++ b/Översikt HERRLJUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44546</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44995</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>45072</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44719</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44895</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>45418</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>44719</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>45373</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45371</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44529</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44525</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>44497</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44533</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44496</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44754</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44659</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44790</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44790</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44601</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44775</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44868</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44638</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44834</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44502</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44519</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44831</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44748</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44538</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45138</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>45756</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44659</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>45350</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45890</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>45335</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45896</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45177</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45153</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45266</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45527</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44811</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45172</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>44900</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>45624</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>44691</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45214</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45009</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45916</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>45723</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45153</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45918</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>45016</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>45357</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45922</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>45922</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45922</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>45922</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45357</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45926</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>44566</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45433</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45603</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45838</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45798</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44980</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45933</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>44942</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44733</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45373</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45425</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>44847</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45138</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>46178</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45365</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45377</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45947</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45950</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45947</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>45086</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45952</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45306</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>46178</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>45952</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45952</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>46182</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>46182</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>46182</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45957</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45957</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45957</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45267</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45267</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45315</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45728</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45317</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>45306</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>44893</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>45159</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>45678</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>46196</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>45587</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45639</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>45978</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>45211</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>45974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>45321</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>45212</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>45618</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>45482</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>45980</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45373</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45468</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>46203</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45327</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45082</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>45985</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>45986</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>45888</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>44904</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>46205</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45986</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45986</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>45643</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45985</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>46029</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>46029</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>45986</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>45989</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>46188</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>45989</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>45993</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>44984</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>45557</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>45760</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>45400</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>45274</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>46013</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>45700</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>45705</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>46282</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>46282</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>46282</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>46031</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>46031</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>46031</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>46031</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>46031</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>46031</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>46031</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>46031</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>46286</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>46035</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>46036</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>46044</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>46043</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>46048</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>45160</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>46288</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>45803</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>45805</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>45708</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45810</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>46246</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>45548</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>45511</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>46294</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>46064</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>46064</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>44533</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>45811</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44942</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>46294</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45345</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>46248</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>46070</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45267</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45337</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>46072</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>46253</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>46296</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45277</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>46295</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>46251</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>46079</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45733</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45736</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>45728</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>45827</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>45728</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>46295</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>46252</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>46071</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>45702</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45476</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45833</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45833</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>46086</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>45834</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45966</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>46091</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>45614</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>46097</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45803</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>46097</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>46097</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>46099</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>46099</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>46097</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>45841</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45841</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>46099</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>45005</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>46301</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>45030</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>45678</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>46114</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>46119</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>46120</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>46304</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>46122</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>46303</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>46128</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>45839</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>45303</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>46130</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>46130</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>46130</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>46129</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>46130</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>44847</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>44918</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45021</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>44917</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>46135</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45265</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>46310</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45897</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>46267</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45664</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45005</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45021</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>46269</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>46267</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45763</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>46272</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>46043</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>44950</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45959</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45565</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>45737</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>46316</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>45728</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>46280</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>46280</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>44860</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>46316</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>46316</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>46280</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>45587</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>45526</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45526</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>46282</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>46142</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>46043</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         <v>45763</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45614</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>46149</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>46149</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44679</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>46154</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45622</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>46154</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45005</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>45273</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45567</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>44890</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>44757</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>44958</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45480</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>44644</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45639</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45615</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>44977</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45099</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45149</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45155</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45713</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45172</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45770</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45077</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>44790</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>44866</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45072</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44524</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45517</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45266</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45233</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45085</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>45084</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>44900</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44882</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45098</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45721</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45771</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45771</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45763</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44908</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44914</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45222</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>44511</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>44952</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>45107</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45247</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>45277</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45327</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45168</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>45163</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>45051</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45453</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>44574</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>45578</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>44524</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>45707</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45176</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45009</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>45595</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45189</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45582</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44525</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45092</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>45763</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45567</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>44551</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45337</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44593</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45196</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45082</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45194</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44665</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45101</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45615</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45660</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44740</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>44686</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>45685</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>44638</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45155</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45621</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>44900</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>45236</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>44686</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45188</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45303</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>44700</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>45756</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45265</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45327</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45271</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>45747</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45736</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45285</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>45562</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>45298</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45219</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45335</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>45546</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>44917</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>44854</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45546</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>45546</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>44890</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>45265</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>45155</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>44605</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>45231</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44628</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>44628</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45369</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45386</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45432</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45531</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45371</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45587</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>45386</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44994</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45888</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45266</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>46070</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>46094</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>46097</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
